--- a/InterTech_Project_Delay_Prediction_Solution.pbix.xlsx
+++ b/InterTech_Project_Delay_Prediction_Solution.pbix.xlsx
@@ -72565,7 +72565,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random Forest Champion Model (72.3% Accuracy, 77.8% AUC)</t>
+          <t>Random Forest Champion Model (72.0% Accuracy, 77.8% AUC)</t>
         </is>
       </c>
     </row>
